--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:32:30+00:00</t>
+    <t>2026-06-25T14:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:37:26+00:00</t>
+    <t>2026-06-25T14:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:37+00:00</t>
+    <t>2026-06-25T14:42:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:42:41+00:00</t>
+    <t>2026-06-25T14:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:50:38+00:00</t>
+    <t>2026-06-25T15:00:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:00:10+00:00</t>
+    <t>2026-06-25T15:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:09:01+00:00</t>
+    <t>2026-06-25T15:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:13:26+00:00</t>
+    <t>2026-06-25T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:13:20+00:00</t>
+    <t>2026-06-25T15:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:16:24+00:00</t>
+    <t>2026-06-25T15:16:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:16:51+00:00</t>
+    <t>2026-06-25T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:17:48+00:00</t>
+    <t>2026-06-25T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:43:40+00:00</t>
+    <t>2026-06-25T15:55:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:55:31+00:00</t>
+    <t>2026-06-25T15:56:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:56:38+00:00</t>
+    <t>2026-06-25T16:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T16:03:47+00:00</t>
+    <t>2026-06-25T16:13:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/mecanisms-mapping/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T16:13:21+00:00</t>
+    <t>2026-06-30T14:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
